--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
@@ -1382,6 +1382,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10, 11, 12A1, 12A2, 12B, 13, 14, 15, 16A, 16B, 16C, 17, 18, 19, 1A, 1B, 2, 20, 21A1, 21A2, 21B1, 21B2, 21C, 21D1A, 21D1B, 21D1C, 21D2, 21E1A, 21E2, 21F10, 21F11, 21F12, 21F13, 21F14, 21F15, 21F1A, 21F1B, 21F1C, 21F1D, 21F2, 21F4, 21F5, 21F6, 21F7, 21F8, 21F9, 21G1, 21G2, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1389,6 +1394,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A, 14B, 15, 16, 17A, 17B, 18, 19, 1A, 1B, 1C, 1D, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1396,6 +1406,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 17A1, 17A2A, 17A2B, 17A2C, 17B1, 17B2A, 17B2B, 17B2BC, 18A1, 18A2, 18B, 1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A1, 2A2, 2B, 3A, 3B, 4, 5A, 5B1, 5B2, 6A, 6B, 7A, 7B, 7C1A, 7C1B, 7C2, 8A, 8B1, 8B2A, 8B2B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1403,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 1A1A, 1A2, 1B, 2A1, 2A2, 2B, 3A1A, 3A1B, 3A2A1, 3A2A2, 3A2B, 3B1, 3B2, 3B3, 4A, 4B, 4C1, 4C2A, 4C2B, 5, 6A, 6B1, 6B2, 6C, 7A, 7B, 8A, 8B, 8C1, 8C2, 9A1A1A1, 9A1A1A2, 9A1A1A3A, 9A1A1B1, 9A1A2, 9A1B, 9A2, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1410,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A, 15B, 16A, 16B, 17A, 17B, 18, 19, 1A, 1B, 20, 2A, 2B, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1417,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1424,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 11, 12A, 12B, 12C1, 12C2, 13, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21, 22A, 22B, 3, 4A, 4B, 5A, 5B, 6, 7, 8A, 8B, 9A, 9B, 9C, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1431,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1438,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1445,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1452,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1459,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1466,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3A, 3B, 3C, 3D, 3E, 3F, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1473,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 2, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1480,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1487,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1494,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13A, 13B, 13C, 13D, 13E, 13F, 14A, 14B, 14C, 14D, 14E, 14F, 14G, 14H, 14I, 15, 16, 17, 18A, 18B, 18C, 18D, 18E, 18F, 19A, 19B, 19C, 19D, 2, 20, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1501,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1508,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1515,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15, 1A, 1B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1522,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6A, 6B1, 6B2, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1529,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1536,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1543,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1550,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 1A1, 1A2, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1557,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1564,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1571,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1578,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1585,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13A, 13B, 13C, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1592,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1599,6 +1754,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B1, 12B2, 12C, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1606,6 +1766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C1A, 11C1B, 11C2, 12, 2, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9A, 9B1, 9B2</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1613,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1620,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1627,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3A, 3B, 3C, 4, 5, 6A, 6B, 6C, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1634,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 1A, 1B, 1C, 1D, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1641,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1648,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3A1, 3A2, 3B1, 3B2, 4, 5A, 5B, 6A, 6B, 6C, 7A, 7B, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1655,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1662,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1669,11 +1874,21 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 11C, 11D, 12, 1A1, 1A2, 1B1, 1B2, 1C1, 1C2, 1C3, 1D, 2, 3, 4A, 4B, 5, 6, 7, 8A, 8B1, 8B2, 8C, 8D, 8E, 9</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
           <t>208</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13A1, 13A2, 13B, 1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
@@ -1898,6 +1898,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 3A, 3B, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1905,6 +1910,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1912,6 +1922,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1919,6 +1934,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 12C, 13, 14, 15, 16, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7A, 7B1, 7B2, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1926,6 +1946,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12A, 12B, 12C, 13, 14A, 14B, 14C, 15A, 15B, 15C, 16, 17, 18A, 18B, 19A, 19B, 1A, 1B1, 1B2, 1B3, 2, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1933,6 +1958,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 2A1A1A, 2A1A1B, 2A1A2, 2A2A, 2A2B, 2A3, 2A3A, 2A3B, 2B, 2C1, 2C2, 2C3, 3A, 3B, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1940,6 +1970,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 10E, 11, 12, 13, 14, 15, 16, 2, 3A, 3A3B, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1947,6 +1982,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A1A, 13A2, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20, 3, 4, 5, 6A, 6B, 7A, 7B, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1954,6 +1994,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1961,6 +2006,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1968,6 +2018,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B1, 10B2, 10C, 10D, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1975,6 +2030,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 3K, 3L, 3M, 3N, 3O, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1982,6 +2042,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1989,6 +2054,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1996,6 +2066,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2003,6 +2078,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2010,6 +2090,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2017,6 +2102,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2024,6 +2114,11 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 2A, 2AA, 2AB, 2AC, 2AD, 2AE, 2AF, 2AG, 2AH, 2AI, 2AJ, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 2K, 2L, 2M, 2N, 2O, 2P, 2Q, 2R, 2S, 2T, 2U, 2V, 2W, 2X, 2Y, 2Z, 4</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2031,6 +2126,11 @@
           <t>226</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2, 3A1A1A, 3A2, 3A3, 3B, 3C, 3D, 4</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2038,6 +2138,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C1, 5C2, 5C3, 5C4, 5C5, 5C6, 5C7, 6A, 6B1, 6B2A, 6B2B, 6B3A, 6B3B, 6B4, 6B5</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2045,6 +2150,11 @@
           <t>228</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A1C1A, 1A1C1B1, 1A1C1B2, 1A1C1C, 1A1C2, 1A1C3, 1A1C4, 1A2, 1B1, 1B2, 1B4, 2A1, 2B1</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2052,6 +2162,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15A, 15B, 16, 17A, 17B, 18A, 18B, 19A, 19B, 19C, 19D, 2, 20A1, 20A2, 20B, 20C, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2059,6 +2174,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2066,6 +2186,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2073,6 +2198,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A, 14B, 14C1, 14C2A, 14C2B, 14D, 14E, 1A, 1B, 1C, 1D, 1E1, 1E2, 1F, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2080,6 +2210,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 1E, 1F, 1G1, 1G2, 1H, 1I, 1J, 1K, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2087,6 +2222,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1A3A, 1A3B, 1A4, 1A5, 1A6, 1B1, 1B2, 2A, 2B1, 2B2, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J1, 2J2</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2094,6 +2234,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E1, 1E2A, 1E2B, 1F, 1G1, 1G2, 1G3, 1G4, 1H, 1I, 2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2101,6 +2246,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2108,6 +2258,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A1A, 5B, 5C1A, 5C1B, 5C2A, 5C2B1A, 5C2B2A, 5C3A, 5C3B1A, 5C3B2, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2115,6 +2270,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>10, 11, 12A1, 12A2, 12B, 13, 14, 15, 16, 17, 18A, 18B, 18C, 18D, 18E, 1A, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G, 2A, 2B, 3A, 3B, 4, 5A1, 5A2, 5B, 5C, 5D, 5E, 5F, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2122,6 +2282,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2129,6 +2294,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2136,6 +2306,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2143,6 +2318,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1, 10B, 11, 12, 13B</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2150,6 +2330,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 1C, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2157,6 +2342,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 1A4, 2</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2164,6 +2354,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2171,6 +2366,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B, 3, 4A1, 4A2A1, 4A2A2, 4A2B, 4A3, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2178,6 +2378,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 2, 6</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2185,6 +2390,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2192,6 +2402,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2199,6 +2414,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 8</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2206,6 +2426,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 10A, 10B, 110, 111, 112, 113, 114, 115, 116, 117, 118, 11A1, 11A2A, 11A2B, 11B, 12A1, 12A2, 12B, 13, 14A, 14B, 14C, 15A, 15B, 15C, 16A, 16B1, 16B2, 17A, 17B, 17C, 18A, 18B, 18C, 18C1A, 18C1B, 18C2, 19A1A1, 19B, 19C, 2, 20A, 20B, 20C1, 20C2, 20D, 20E, 20F, 21A1, 21A2, 21B, 21C1, 21C2, 21D, 21E, 22A, 22B, 22C1A, 22C2, 23, 24A1, 24A2, 24B, 24C, 25A1A, 25A1B, 25A1C, 25A2, 25B, 26A, 26B, 26C, 27A1, 27A2, 27A3, 27A4, 27B, 28A, 28B, 29A, 29B, 29C, 30A, 30B, 31A1A, 31A1B, 31A2, 31B, 32A1, 32B, 32C1, 32C2, 33, 34A1A1, 34A1B, 34A2, 34A3A, 34A3B, 34A3C, 34A3D1, 34A3D2, 34B, 34C, 35A, 35B, 36A, 36B, 36C1A, 36C1B, 36C2, 37A, 37B1, 37B2, 37B3, 38A, 38B1A, 38B2, 39A1, 39B, 39C, 3A1, 3A1A2, 3A1B, 3A2, 3B, 3C, 3D, 3E, 3F, 40, 41A, 41B, 42A, 42B1, 42B2, 43A, 43B1, 43B2, 44A1, 44A2, 44B, 44C, 44D, 45A1, 45A2, 45B, 45C, 45D, 46A1, 46A2, 46A3, 46B, 46C, 47A, 47B, 47C1, 47C2, 48A, 48B, 48C, 49A1, 49A2, 49B, 49C, 4A1, 4A2, 4B, 5, 50A, 50B1, 50B2, 51, 52, 53A, 53B, 53C, 54A, 54B, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67A1, 67A2A, 67A2B, 67A2C, 67A3, 67B, 68A1A1, 68A1B1, 68A1B2, 68A2, 68B, 69A, 69B, 69C, 6A, 6B, 7, 70, 71A1, 71A2, 71B, 71C, 71D1, 71D2, 72A1A, 72A2, 72B1, 72B2, 73A1A, 73A2, 73B, 74, 75, 76A, 76B1, 76B2, 77, 78, 79, 80, 81, 82, 83A, 83B, 84A1, 84A2A, 84A2B, 84A3, 84B, 85A1A, 85A2, 85B1A, 85B1B, 85B1C, 85B2A, 85B2B, 86, 87, 88A, 88B, 89A, 89B, 8A1A, 8A2, 8A3, 8B, 90, 91A, 91B, 92, 93, 94, 95A, 95B, 95C, 95D, 95E, 96, 97, 98, 99, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2213,6 +2438,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2220,6 +2450,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 4</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2227,6 +2462,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2234,6 +2474,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2241,6 +2486,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2248,6 +2498,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2255,6 +2510,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2262,6 +2522,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2269,6 +2534,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2276,6 +2546,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2283,6 +2558,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2290,6 +2570,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2297,6 +2582,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2304,6 +2594,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2311,6 +2606,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2318,6 +2618,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2325,6 +2630,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2332,6 +2642,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2339,6 +2654,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2346,6 +2666,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2353,6 +2678,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2360,6 +2690,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2367,6 +2702,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2374,6 +2714,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2381,6 +2726,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2388,6 +2738,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2395,6 +2750,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2402,6 +2762,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>-, 14, 7</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2409,6 +2774,11 @@
           <t>275</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1, 13</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2416,6 +2786,11 @@
           <t>276</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 8</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2423,6 +2798,11 @@
           <t>277</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2430,6 +2810,11 @@
           <t>278</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2437,6 +2822,11 @@
           <t>279</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2444,6 +2834,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2451,6 +2846,11 @@
           <t>280</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 7</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2458,6 +2858,11 @@
           <t>281</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1, 2, 9</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2465,6 +2870,11 @@
           <t>282</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2472,6 +2882,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1, 5</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2479,6 +2894,11 @@
           <t>284</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2486,6 +2906,11 @@
           <t>285</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2493,6 +2918,11 @@
           <t>286</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1A10, 1A11, 1A12, 1A13, 1A14, 1A15, 1A16, 1A17, 1A18, 1A19, 1A1A1A, 1A1A2, 1A1B, 1A1C, 1A1D, 1A2, 1A20A, 1A20B, 1A21A, 1A3, 1A4, 1A5, 1A6A, 1A6B, 1A7, 1A8A, 1A8B, 1A9, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 1M, 1N1, 1N2, 1O, 1P, 2, 22, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 3A1, 3A10, 3A1A1B, 3A1A2, 3A1B, 3A2, 3A3, 3A4, 3A5, 3A6, 3A7, 3A8A, 3A9A, 3A9B, 3B1, 3B2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2500,6 +2930,11 @@
           <t>287</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2507,6 +2942,11 @@
           <t>288</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A1, 11A2, 11B, 12A, 12B, 13A1, 13A2, 13B, 14A, 14B, 15A, 15B, 16, 17A, 17B, 18, 19, 1A, 1B, 2A, 2B, 2C, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2514,6 +2954,11 @@
           <t>289</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B1A, 2B1B, 2B1C, 2B2, 3A1A, 3A1B, 3A1C, 3A1D, 3A1E, 3A1F, 3A2, 3A3A, 3A3B, 3A3C, 3A3D, 3A3E, 3A3F, 3A3G, 3A3H, 3A3I, 3A3J, 3A4, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2521,6 +2966,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2528,6 +2978,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14A, 14B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2535,6 +2990,11 @@
           <t>291</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2542,6 +3002,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A1, 2A2, 2A3, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2549,6 +3014,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5A, 5B, 5C, 6A, 6B1, 6B2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2556,6 +3026,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>10A, 10B, 1A, 1B1, 1B2, 1B3, 1B4, 1B5, 2, 3, 4A, 4B, 5A, 5B, 6A, 6B, 7A, 7B, 7C, 7D, 8A, 8B, 8C, 8D, 8E, 9A, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2563,6 +3038,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10B, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 19, 1A, 1B1, 1B2, 20, 2A, 2B1, 2B2, 2B3, 3A, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2570,11 +3050,21 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B1, 1B2A, 1B2B, 1B3A, 1B3B, 1B4, 1C1, 1C2A1A, 1C2A2, 1C2B, 1C2C, 1C2D1, 1D1, 1D2, 1E, 1F, 1G, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
           <t>297</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 2A, 2B, 2C1B, 2C2, 2CA1</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
@@ -3074,6 +3074,11 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13A, 13B, 14A, 14B, 15A, 15B, 16A, 16B, 17A1, 17A2, 17B, 18A, 18B, 19A, 19B, 2, 20A, 20B, 3, 4, 5, 6A, 6B, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3081,6 +3086,11 @@
           <t>299</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12A, 12B, 12C, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3088,6 +3098,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 20, 2A1, 2A2, 2B, 2C, 3A, 3B1, 3B2, 4A, 4B1, 4B2, 4B3, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3095,6 +3110,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 18, 2, 3A1A1A, 3A2, 3B, 4, 5, 6A, 6B, 7, 8A, 8B, 8C, 8D, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3102,6 +3122,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3109,6 +3134,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14A1, 14A2, 14B, 2, 3, 4A, 4B, 5, 6A, 6B, 7A1, 7A2, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3116,6 +3146,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3123,6 +3158,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3130,6 +3170,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3137,6 +3182,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3144,6 +3194,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3151,6 +3206,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3158,6 +3218,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3165,6 +3230,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3172,6 +3242,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2A, 2B, 2C, 3, 4, 5, 6A, 6B, 6C, 7, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3179,6 +3254,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3186,6 +3266,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 2A, 2B, 2C, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3193,6 +3278,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 6A, 6B, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3200,6 +3290,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3207,6 +3302,11 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 17, 18, 19, 1A, 1B10, 1B11, 1B12, 1B13, 1B14, 1B15, 1B16, 1B17, 1B18, 1B19, 1B1A, 1B1A10A, 1B1A11, 1B1A12, 1B1A13, 1B1A14, 1B1A1A1, 1B1A1A2, 1B1A1A3, 1B1A1B, 1B1A1C, 1B1A2, 1B1A3, 1B1A4, 1B1A5, 1B1A6, 1B1A7, 1B1A8, 1B1A9A, 1B1A9B, 1B1B, 1B1C, 1B1D, 1B1E, 1B1F, 1B1G, 1B1H, 1B1I, 1B1J, 1B1K, 1B1L, 1B1M, 1B2, 1B20, 1B21, 1B3, 1B4, 1B5, 1B6, 1B7, 1B8, 1B9, 1C, 2, 20A, 20B, 21, 22, 23, 24, 25A, 25B, 25C, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A1A, 3A1A1B, 3A1A1C, 3A1B, 3A1C1, 3A1D, 3A2A, 3A2B, 3A3A1A1, 3A3B, 3B1, 3B2, 3B3, 40, 41, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3214,6 +3314,11 @@
           <t>315</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B1, 11B2, 11B3A, 11B3B, 12A, 12B, 12C1, 12C2, 13A, 13B, 13C, 13D1, 13D2, 13E, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 19C, 19D, 2, 20A, 20B, 21, 22, 23A, 23B, 24A1, 24B, 25, 26A, 26B, 27A, 27B, 28A, 28B, 28C, 28D, 29A1, 29A2, 29B, 3, 30, 31A, 31B, 32, 33, 34, 35, 36, 37, 38A, 38B, 39, 40, 41, 42, 43, 44A1A, 44A1B, 44A2, 44B, 45, 46, 47, 48A, 48B, 49A, 49B, 4A1A1, 4A1A1A2, 4A1A2, 4A1B, 4A2B, 4A2C, 4B10, 4B11, 4B12, 4B13, 4B1A1, 4B2, 4B3, 4B4, 4B5, 4B6, 4B7, 4B8, 4B9, 50, 51, 52A, 52B, 53, 54, 55A, 55B, 56, 57, 58, 59, 5A1A, 5A1B, 5A2, 5B, 60, 61, 62, 63, 64, 65, 66, 67, 68A, 68B, 69, 6A1, 6A2, 6B, 6C, 6D, 6E, 6F, 6G, 6H, 6I, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 7A, 7B1, 7B2, 7B3, 7B4, 7B5, 8A, 8B, 8C, 8D, 9</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3221,6 +3326,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10B, 11, 12, 13, 14, 15, 15C, 16A, 16B, 17, 18, 19, 1A10, 1A11A, 1A11B, 1A12, 1A13, 1A14, 1A1A1A, 1A1A1B, 1A1A1C, 1A1A2, 1A1A3, 1A1B, 1A1C, 1A1D, 1A1E, 1A1F1, 1A1F2, 1A2, 1A3, 1A4, 1A5, 1A6, 1A7, 1A8, 1A9, 1B1A, 1B1B, 1B2, 1B3, 1C1A1, 1C1B1, 1C1B2, 1C2, 20, 21, 22, 23A, 23B, 24, 25, 26, 27, 28, 29, 2A1A, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A, 3A1B, 3A1C, 3A1D, 3A1E1A1, 3A1E2A, 3A1E3A, 3A1E3B, 3A1E4, 3A2A1, 3A2B, 3A3, 3A4, 3A5, 3A6, 3B1, 3B2, 3C, 3D, 3E, 3F, 3G, 3H, 3I1, 3I2, 3J, 3K1A, 3K2, 3L, 40, 41, 42, 43, 44, 45A1A, 45A1B, 45A1C, 45A2, 45B1, 45B2, 46, 47, 48, 49, 4A, 4B, 50, 51, 52, 53A, 53B, 54, 55, 56, 57, 58, 59, 5A1A, 5A1B, 5A2, 5A3, 5B1, 5B2, 5B3, 60, 61, 62, 63A, 63B, 64, 6A1A1, 6A1B, 6A2A, 6A2B, 6B1A1, 6B1B, 6B2, 6B3, 6B4, 6B5, 6B6, 6C1, 6C2A, 6C2B, 7A, 7B1A, 7B1B1, 7B1B2, 7B2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3228,6 +3338,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13A, 13B, 14, 15, 16, 17, 18, 19A1, 19A2, 19A3A1, 19A3A2, 19A3B, 19B, 19C, 19D, 19E, 19F, 19G, 19H, 2, 20, 21, 22, 23, 24A, 24B1, 24B2, 24B3, 25A1, 25A2, 25A3, 25A4, 25A5, 25A6, 25A7, 25B, 25C, 25D, 26A1, 26A2, 26B1, 26B2, 27A1, 27A2A, 27A2B, 27B1, 27B2, 27C1, 27C2, 27D, 27E, 28A, 28B1, 28B2, 28C1, 28C2A, 28C2B, 28C2C, 28C3A, 28C3B, 28C4, 28C5, 29A, 29B1, 29B2, 3, 30A, 30B1, 30B2, 31, 32, 33A1, 33A2, 33B1, 33B2, 33B3, 33B4, 33C, 33D, 33E, 33F, 33G, 33H, 34A1, 34A2, 34A3, 34B, 35A, 35B, 36A, 36B, 37, 38, 39, 4, 40, 41A1, 41A2, 41B, 42, 43, 44, 45A1A, 45A1B, 45A1C, 45A1D, 45A2, 45B, 46, 47, 48, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3235,6 +3350,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 2, 3A1, 3A2, 3B, 3C, 3D, 3E, 3F, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3242,6 +3362,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1, 2, 3A1, 3A2, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3249,6 +3374,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6A1, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3256,6 +3386,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 2, 3A, 3B1, 3B2, 4A1, 4A2, 4B, 4C, 4D, 5A1, 5A2, 5A3A, 5A3B, 5A4, 5B, 5C1A, 5C1B, 5C1C, 5C2</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3263,6 +3398,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3270,6 +3410,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13B2, 14, 15A1, 15A2, 15B, 16, 17, 18, 19, 1A1, 1A1B, 1A2, 1A3, 1A4, 1A5, 1A6, 1B1, 1C, 1D, 1E, 1F, 1G1, 1G2, 1H, 1I, 20A, 20B, 21, 22, 23, 24A, 24B, 25A, 25B, 26, 27, 28, 29, 2A, 2B, 2C, 30A, 30B, 7A, 7A2, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3277,6 +3422,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 14A1, 14A2, 14B, 15, 16, 17, 18, 19, 1A1, 1A2A10, 1A2A11, 1A2A12, 1A2A13, 1A2A1A, 1A2A1B1, 1A2A1B2, 1A2A1B3, 1A2A2, 1A2B, 1A2C, 1A2D, 1A2E, 1A2F, 1A2G, 1A2H, 1A2I, 1A2J, 1B1A, 1B1B1, 1B1B2, 1B1C, 1B1D1A, 1B1D1B, 1B1D2, 1B2, 1B3, 1B4, 1C1, 1C2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 3, 30, 31, 32A, 32B, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 47, 49A1A, 49A2, 49B, 5, 50, 51, 52, 53, 54, 55A, 55B, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65A, 65B, 66, 67, 68, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3284,6 +3434,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 4C1, 4C2, 5</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3291,6 +3446,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3298,6 +3458,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3305,6 +3470,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1, 15, 16</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3312,6 +3482,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>10, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 11, 110, 111, 112, 113, 114, 115, 116, 117, 118, 119, 12, 120, 121, 122, 123, 124, 125, 126, 127, 128, 129, 13, 130, 131, 132, 133, 134, 135, 136, 137, 138, 139, 14, 140, 141, 142, 143, 144, 145, 146, 147, 148, 149, 15, 150, 151, 152, 153, 154, 155, 156, 157, 158, 159, 16, 160, 161, 162, 163, 164, 165, 166, 167, 168, 169, 17, 170, 171, 172, 173, 174, 175, 176, 177, 178, 179, 18, 180, 181, 182, 183, 184, 185, 186, 187, 188, 189, 19, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 1A1A, 1A2, 2, 20, 200, 201, 202, 203, 204, 205, 206, 207, 208, 209, 21, 210A, 210B, 211, 212, 213, 214, 215, 216, 217, 218, 219, 22, 220, 221, 222, 223, 224, 225, 226, 227, 228, 229, 23, 230, 231, 232, 233, 234, 235, 236, 237, 238, 239, 24, 240, 241, 242, 243, 244, 245, 246, 247, 248, 249, 25, 250, 251, 252, 253, 254, 255, 256, 257, 258, 259, 26, 260, 261, 262, 263, 264, 265, 266, 267, 268, 269, 27, 270, 271, 272, 273, 274, 275, 276, 277, 278, 279, 28, 280, 281, 282, 283, 284, 285, 286, 287, 288, 289, 29, 290, 291, 292, 293, 294, 295, 296, 297, 298, 299, 3, 30, 300, 301, 302, 303, 304, 305, 306, 307, 308, 309, 31, 310, 311, 312, 313, 314, 315, 316, 317, 318, 319, 32, 320, 321, 322, 323, 324, 325, 326, 327, 328, 329, 33, 330, 331, 332, 333, 334, 335, 336, 337, 338, 339, 34, 340, 341, 342, 343, 344, 345, 346, 347, 348, 349, 35, 350, 351, 352, 353, 354, 355, 356, 357, 358, 359, 36, 360, 361, 362, 363, 364, 365A, 365B, 366A, 366B, 367A, 367B, 368, 369, 37, 370, 371, 372, 373, 374, 375, 376, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 8, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3319,6 +3494,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1, 10A1, 10A2, 10B, 11A, 11B, 12, 13A1, 13A2, 13B, 14A1, 14A2, 14B, 15, 16, 17A1, 17A2, 17B, 2, 3, 4A1, 4A2, 4B, 5A, 5B, 6A, 7A, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3326,6 +3506,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3333,6 +3518,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 2</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3340,6 +3530,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A1, 3A2, 3B, 3C, 4A1, 4A2, 4B, 5, 6A, 9A</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3347,6 +3542,11 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 2, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3354,6 +3554,11 @@
           <t>333</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 6A, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3361,6 +3566,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3368,6 +3578,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3375,6 +3590,11 @@
           <t>336</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3382,6 +3602,11 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3389,6 +3614,11 @@
           <t>338</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3396,6 +3626,11 @@
           <t>339</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3403,6 +3638,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3410,6 +3650,11 @@
           <t>340</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 2A1A, 2A1A1, 2A1B, 2A2B1, 2A2C1, 2A3A1, 2A3B1A, 2A3B1B1, 2A3B1C1, 2A3B2A, 2A4A, 2A4B, 2B, 2C, 2D1, 2D2A, 2D2B, 3A1, 3A2, 3B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3417,6 +3662,11 @@
           <t>341</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1, 2, 5B, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3424,6 +3674,11 @@
           <t>342</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2A, 1A2B, 1B, 2, 6A1A, 6A1B, 6A2A, 6A2B1, 6A2B2, 6B, 6C, 7A, 8A1, 8A2, 8B, 8D, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3431,6 +3686,11 @@
           <t>343</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A, 1A3B, 1A3C, 1A3D, 1A3E, 1A3F, 1A3G, 1A3H, 1A3I, 1B, 1C, 1D, 1E1, 1E2, 2, 3A1A, 3A2A1, 4, 5A, 5B, 5C1, 5C2, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3438,6 +3698,11 @@
           <t>344</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3445,6 +3710,11 @@
           <t>345</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3452,6 +3722,11 @@
           <t>346</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3459,6 +3734,11 @@
           <t>347</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3466,6 +3746,11 @@
           <t>348</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3473,6 +3758,11 @@
           <t>349</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3480,6 +3770,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3487,6 +3782,11 @@
           <t>350</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3494,6 +3794,11 @@
           <t>351</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3501,6 +3806,11 @@
           <t>352</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3508,6 +3818,11 @@
           <t>353</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3515,6 +3830,11 @@
           <t>354</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3522,6 +3842,11 @@
           <t>355</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3529,6 +3854,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3536,6 +3866,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3543,6 +3878,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3550,6 +3890,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3557,6 +3902,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3564,6 +3914,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3571,6 +3926,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B1, 2B2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3578,6 +3938,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3585,6 +3950,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3592,6 +3962,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5A, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3599,6 +3974,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3606,6 +3986,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3613,11 +3998,21 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
           <t>48</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
@@ -4022,6 +4022,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 3, 4A, 4B, 5, 6A, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -4029,6 +4034,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6A, 6B, 6C, 6D, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -4036,6 +4046,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -4043,6 +4058,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -4050,6 +4070,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -4057,6 +4082,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 19, 2A, 2B, 3A1, 3A2, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 3K, 3L, 3M, 3N, 3O, 3P, 3Q, 3R, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -4064,6 +4094,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -4071,6 +4106,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -4078,6 +4118,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -4085,6 +4130,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -4092,6 +4142,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -4099,6 +4154,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3A, 3B, 4, 5A, 5B, 6, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -4106,6 +4166,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -4113,6 +4178,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B1, 3B2, 4A, 4B, 5A1, 5A2, 5A3, 5B, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -4120,6 +4190,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4127,6 +4202,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -4134,6 +4214,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -4141,6 +4226,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -4148,6 +4238,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -4155,6 +4250,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -4162,6 +4262,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4169,6 +4274,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4176,6 +4286,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4183,6 +4298,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4190,6 +4310,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4197,6 +4322,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 14, 15A, 15B, 1A, 1B, 1C, 2, 3A, 3B, 3C, 3D, 3E, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4204,6 +4334,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3A1, 3A2, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4211,6 +4346,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4218,6 +4358,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4225,6 +4370,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4232,6 +4382,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B, 2A2, 2A3, 2A4, 2A5, 2A6, 2B, 2C, 2D1, 2D2, 2E, 2F, 2G1A, 2G1B, 2G2, 2H, 2I, 2J</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4239,6 +4394,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4246,6 +4406,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15, 16, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4253,6 +4418,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4260,6 +4430,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4267,6 +4442,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4274,6 +4454,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4A, 4B, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4281,6 +4466,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1, 105, 106, 107, 108, 109, 10A1, 10A2, 10B, 11, 110, 111, 112, 113, 114, 115, 116, 117, 118, 119, 12, 13, 14A, 14B, 14C, 15A1, 15A1B, 15A1C, 15A1D, 15A2, 15A3, 15A4, 15A5A, 15A5B, 15A5C, 15A6, 15A7, 15A8, 15B, 16, 17A1, 17A2, 17B, 17C, 17D, 17E, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46A, 46B, 47A, 47B, 48A, 48B, 48C, 49A, 49B, 5, 6, 7A, 7B1, 7B2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4288,6 +4478,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 1A2A, 1B, 2, 20, 21A1, 21A2, 21B, 22, 23, 24, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4295,6 +4490,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 10E, 10F, 10G, 10H, 10I, 10J, 10K, 10L, 10M, 10N, 10P, 10Q, 10R, 10S, 10T, 10U, 10V, 11, 12A, 12B, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4302,6 +4502,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4309,6 +4514,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4316,6 +4526,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2A, 2B, 2C, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4323,6 +4538,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 2, 3A, 3B, 4A1, 4A2, 4B, 5, 6A, 6B, 7, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4330,6 +4550,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1A10, 1A11, 1A1A, 1A2, 1A3, 1A4, 1A5, 1A6, 1A7, 1A8, 1A9, 1B, 1C, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4337,6 +4562,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 1E, 1F, 1G, 1H, 1I1, 1I2, 1J, 1K, 1L, 1M, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4344,6 +4574,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -4351,11 +4586,21 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17A, 17B, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
           <t>92</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 2, 3, 4A, 4B, 4C, 4D, 4E, 4F, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pappankuppam_13.426655_80.093237.xlsx
@@ -4610,6 +4610,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4617,6 +4622,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -4624,6 +4634,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -4631,6 +4646,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -4638,6 +4658,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -4645,11 +4670,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>
